--- a/templates/invoice_template.xlsx
+++ b/templates/invoice_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preve\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0649A7-6CAA-4416-8DA5-E17CE229480C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479E32A6-3D21-40C1-888B-D2CBA09E1E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="TDSheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">TDSheet!$A$1:$AL$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TDSheet!$A$1:$AL$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -511,117 +511,117 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -644,16 +644,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>28200</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>117100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -674,8 +674,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1158240" y="5974080"/>
-          <a:ext cx="1645920" cy="1476000"/>
+          <a:off x="2101850" y="5892800"/>
+          <a:ext cx="1657350" cy="1450600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -690,16 +690,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180340</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>113340</xdr:rowOff>
+      <xdr:rowOff>100640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>6660</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>102870</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -720,8 +720,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2308860" y="5957880"/>
-          <a:ext cx="838200" cy="563880"/>
+          <a:off x="1717040" y="5904540"/>
+          <a:ext cx="843280" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -869,7 +869,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="10"/>
+      <c r="B1" s="47"/>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -987,52 +987,52 @@
     </row>
     <row r="4" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="2:38" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="21" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="41" t="s">
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="14"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="16"/>
+      <c r="AK5" s="16"/>
+      <c r="AL5" s="18"/>
     </row>
     <row r="6" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="27"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -1050,14 +1050,14 @@
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="37" t="s">
+      <c r="T6" s="35"/>
+      <c r="U6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="32" t="s">
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="44" t="s">
         <v>4</v>
       </c>
       <c r="Z6" s="11"/>
@@ -1072,96 +1072,96 @@
       <c r="AI6" s="11"/>
       <c r="AJ6" s="11"/>
       <c r="AK6" s="11"/>
-      <c r="AL6" s="28"/>
+      <c r="AL6" s="35"/>
     </row>
     <row r="7" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="17"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="17"/>
-      <c r="AF7" s="17"/>
-      <c r="AG7" s="17"/>
-      <c r="AH7" s="17"/>
-      <c r="AI7" s="17"/>
-      <c r="AJ7" s="17"/>
-      <c r="AK7" s="17"/>
-      <c r="AL7" s="30"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="13"/>
+      <c r="AJ7" s="13"/>
+      <c r="AK7" s="13"/>
+      <c r="AL7" s="14"/>
     </row>
     <row r="8" spans="2:38" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="21" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="12" t="s">
+      <c r="V8" s="52"/>
+      <c r="W8" s="52"/>
+      <c r="X8" s="53"/>
+      <c r="Y8" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="13"/>
-      <c r="AJ8" s="13"/>
-      <c r="AK8" s="13"/>
-      <c r="AL8" s="14"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="18"/>
     </row>
     <row r="9" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="27"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -1179,14 +1179,14 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="37" t="s">
+      <c r="T9" s="35"/>
+      <c r="U9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="32"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="44"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
@@ -1199,125 +1199,125 @@
       <c r="AI9" s="11"/>
       <c r="AJ9" s="11"/>
       <c r="AK9" s="11"/>
-      <c r="AL9" s="28"/>
+      <c r="AL9" s="35"/>
     </row>
     <row r="10" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="17"/>
-      <c r="AL10" s="30"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="13"/>
+      <c r="AH10" s="13"/>
+      <c r="AI10" s="13"/>
+      <c r="AJ10" s="13"/>
+      <c r="AK10" s="13"/>
+      <c r="AL10" s="14"/>
     </row>
     <row r="11" spans="2:38" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="48" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="39" t="s">
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="37" t="s">
+      <c r="L11" s="16"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="26" t="s">
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="18"/>
+      <c r="Y11" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="13"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="14"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="18"/>
     </row>
     <row r="12" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="27"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="34"/>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="27"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="34"/>
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
@@ -1330,10 +1330,10 @@
       <c r="AI12" s="11"/>
       <c r="AJ12" s="11"/>
       <c r="AK12" s="11"/>
-      <c r="AL12" s="28"/>
+      <c r="AL12" s="35"/>
     </row>
     <row r="13" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="27"/>
+      <c r="B13" s="34"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -1352,11 +1352,11 @@
       <c r="R13" s="11"/>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
-      <c r="U13" s="27"/>
+      <c r="U13" s="34"/>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="27"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="34"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
@@ -1369,52 +1369,52 @@
       <c r="AI13" s="11"/>
       <c r="AJ13" s="11"/>
       <c r="AK13" s="11"/>
-      <c r="AL13" s="28"/>
+      <c r="AL13" s="35"/>
     </row>
     <row r="14" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="17"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="17"/>
-      <c r="AK14" s="17"/>
-      <c r="AL14" s="30"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="13"/>
+      <c r="AG14" s="13"/>
+      <c r="AH14" s="13"/>
+      <c r="AI14" s="13"/>
+      <c r="AJ14" s="13"/>
+      <c r="AK14" s="13"/>
+      <c r="AL14" s="14"/>
     </row>
     <row r="15" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="50" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="11"/>
@@ -1494,48 +1494,48 @@
       <c r="AL17" s="11"/>
     </row>
     <row r="18" spans="1:38" s="1" customFormat="1" ht="6.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="50"/>
-      <c r="V18" s="50"/>
-      <c r="W18" s="50"/>
-      <c r="X18" s="50"/>
-      <c r="Y18" s="50"/>
-      <c r="Z18" s="50"/>
-      <c r="AA18" s="50"/>
-      <c r="AB18" s="50"/>
-      <c r="AC18" s="50"/>
-      <c r="AD18" s="50"/>
-      <c r="AE18" s="50"/>
-      <c r="AF18" s="50"/>
-      <c r="AG18" s="50"/>
-      <c r="AH18" s="50"/>
-      <c r="AI18" s="50"/>
-      <c r="AJ18" s="50"/>
-      <c r="AK18" s="50"/>
-      <c r="AL18" s="50"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="31"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="31"/>
+      <c r="AK18" s="31"/>
+      <c r="AL18" s="31"/>
     </row>
     <row r="19" spans="1:38" s="1" customFormat="1" ht="6.9" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="45" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="11"/>
@@ -1580,7 +1580,7 @@
     <row r="21" spans="1:38" s="1" customFormat="1" ht="6.9" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="45" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="11"/>
@@ -1624,159 +1624,159 @@
     </row>
     <row r="23" spans="1:38" s="1" customFormat="1" ht="6.9" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:38" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="45" t="s">
+      <c r="C24" s="24"/>
+      <c r="D24" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="45" t="s">
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="45" t="s">
+      <c r="T24" s="24"/>
+      <c r="U24" s="24"/>
+      <c r="V24" s="24"/>
+      <c r="W24" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="45" t="s">
+      <c r="X24" s="24"/>
+      <c r="Y24" s="24"/>
+      <c r="Z24" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="AA24" s="46"/>
-      <c r="AB24" s="46"/>
-      <c r="AC24" s="46"/>
-      <c r="AD24" s="46"/>
-      <c r="AE24" s="46"/>
-      <c r="AF24" s="53" t="s">
+      <c r="AA24" s="24"/>
+      <c r="AB24" s="24"/>
+      <c r="AC24" s="24"/>
+      <c r="AD24" s="24"/>
+      <c r="AE24" s="24"/>
+      <c r="AF24" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="AG24" s="46"/>
-      <c r="AH24" s="46"/>
-      <c r="AI24" s="46"/>
-      <c r="AJ24" s="46"/>
-      <c r="AK24" s="54"/>
+      <c r="AG24" s="24"/>
+      <c r="AH24" s="24"/>
+      <c r="AI24" s="24"/>
+      <c r="AJ24" s="24"/>
+      <c r="AK24" s="43"/>
     </row>
     <row r="25" spans="1:38" ht="43.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
-      <c r="B25" s="18">
+      <c r="B25" s="21">
         <v>1</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="44" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="38">
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="37">
         <v>1</v>
       </c>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="51" t="s">
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16"/>
       <c r="Z25" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="AA25" s="13"/>
-      <c r="AB25" s="13"/>
-      <c r="AC25" s="13"/>
-      <c r="AD25" s="13"/>
-      <c r="AE25" s="13"/>
-      <c r="AF25" s="24" t="e">
+      <c r="AA25" s="16"/>
+      <c r="AB25" s="16"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="40" t="e">
         <f>S25*Z25</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="13"/>
-      <c r="AH25" s="13"/>
-      <c r="AI25" s="13"/>
-      <c r="AJ25" s="13"/>
-      <c r="AK25" s="25"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="16"/>
+      <c r="AI25" s="16"/>
+      <c r="AJ25" s="16"/>
+      <c r="AK25" s="41"/>
       <c r="AL25" s="3"/>
     </row>
     <row r="26" spans="1:38" ht="43.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
-      <c r="B26" s="18">
+      <c r="B26" s="21">
         <v>2</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="44" t="s">
+      <c r="C26" s="16"/>
+      <c r="D26" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="S26" s="38">
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="37">
         <v>1</v>
       </c>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="51" t="s">
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16"/>
       <c r="Z26" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="24" t="e">
+      <c r="AA26" s="16"/>
+      <c r="AB26" s="16"/>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="40" t="e">
         <f>S26*Z26</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG26" s="13"/>
-      <c r="AH26" s="13"/>
-      <c r="AI26" s="13"/>
-      <c r="AJ26" s="13"/>
-      <c r="AK26" s="25"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="16"/>
+      <c r="AI26" s="16"/>
+      <c r="AJ26" s="16"/>
+      <c r="AK26" s="41"/>
       <c r="AL26" s="3"/>
     </row>
     <row r="27" spans="1:38" s="1" customFormat="1" ht="6.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1826,7 +1826,7 @@
       <c r="AE28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AF28" s="35" t="e">
+      <c r="AF28" s="10" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
@@ -1845,7 +1845,7 @@
       <c r="AE29" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AF29" s="35" t="s">
+      <c r="AF29" s="10" t="s">
         <v>33</v>
       </c>
       <c r="AG29" s="11"/>
@@ -1863,7 +1863,7 @@
       <c r="AE30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AF30" s="35" t="e">
+      <c r="AF30" s="10" t="e">
         <f>SUM(AF28:AK29)</f>
         <v>#VALUE!</v>
       </c>
@@ -1874,7 +1874,7 @@
       <c r="AK30" s="11"/>
     </row>
     <row r="31" spans="1:38" ht="11.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="28" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="11"/>
@@ -2042,23 +2042,23 @@
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="S36" s="42" t="s">
+      <c r="S36" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
-      <c r="Z36" s="17"/>
-      <c r="AA36" s="17"/>
-      <c r="AB36" s="17"/>
-      <c r="AC36" s="17"/>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="17"/>
-      <c r="AF36" s="17"/>
-      <c r="AG36" s="17"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
     </row>
     <row r="37" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="9"/>
@@ -2069,7 +2069,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
-      <c r="J37" s="31" t="s">
+      <c r="J37" s="36" t="s">
         <v>39</v>
       </c>
       <c r="K37" s="11"/>
@@ -2080,7 +2080,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
       <c r="R37" s="9"/>
-      <c r="S37" s="31" t="s">
+      <c r="S37" s="36" t="s">
         <v>40</v>
       </c>
       <c r="T37" s="11"/>
@@ -2111,21 +2111,21 @@
       <c r="O39" s="8"/>
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
-      <c r="Z39" s="17"/>
-      <c r="AA39" s="17"/>
-      <c r="AB39" s="17"/>
-      <c r="AC39" s="17"/>
-      <c r="AD39" s="17"/>
-      <c r="AE39" s="17"/>
-      <c r="AF39" s="17"/>
-      <c r="AG39" s="17"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="13"/>
     </row>
     <row r="40" spans="2:38" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="9"/>
@@ -2136,7 +2136,7 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
-      <c r="J40" s="31" t="s">
+      <c r="J40" s="36" t="s">
         <v>39</v>
       </c>
       <c r="K40" s="11"/>
@@ -2147,7 +2147,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="9"/>
-      <c r="S40" s="31" t="s">
+      <c r="S40" s="36" t="s">
         <v>40</v>
       </c>
       <c r="T40" s="11"/>
@@ -2172,14 +2172,38 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="AF29:AK29"/>
-    <mergeCell ref="B10:T10"/>
-    <mergeCell ref="Z26:AE26"/>
-    <mergeCell ref="U9:X10"/>
-    <mergeCell ref="G20:AL20"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="W26:Y26"/>
-    <mergeCell ref="S24:V24"/>
+    <mergeCell ref="B1:AL3"/>
+    <mergeCell ref="Y8:AL8"/>
+    <mergeCell ref="Z25:AE25"/>
+    <mergeCell ref="S39:AG39"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B16:AL17"/>
+    <mergeCell ref="G22:AL22"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="B32:AJ32"/>
+    <mergeCell ref="Y11:AL14"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="Y6:AL7"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="U5:X5"/>
+    <mergeCell ref="B12:T13"/>
+    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="B8:T9"/>
+    <mergeCell ref="U11:X14"/>
+    <mergeCell ref="J40:Q40"/>
+    <mergeCell ref="S40:AG40"/>
+    <mergeCell ref="S26:V26"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="M11:T11"/>
+    <mergeCell ref="S25:V25"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Y9:AL10"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B14:T14"/>
     <mergeCell ref="Y5:AL5"/>
     <mergeCell ref="S36:AG36"/>
     <mergeCell ref="B7:T7"/>
@@ -2196,41 +2220,17 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="W24:Y24"/>
     <mergeCell ref="B5:T6"/>
-    <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="B8:T9"/>
-    <mergeCell ref="U11:X14"/>
-    <mergeCell ref="J40:Q40"/>
-    <mergeCell ref="S40:AG40"/>
-    <mergeCell ref="S26:V26"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="M11:T11"/>
-    <mergeCell ref="S25:V25"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="Y9:AL10"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B14:T14"/>
-    <mergeCell ref="B1:AL3"/>
-    <mergeCell ref="Y8:AL8"/>
-    <mergeCell ref="Z25:AE25"/>
-    <mergeCell ref="S39:AG39"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B16:AL17"/>
-    <mergeCell ref="G22:AL22"/>
-    <mergeCell ref="U8:X8"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="B32:AJ32"/>
-    <mergeCell ref="Y11:AL14"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="Y6:AL7"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="B12:T13"/>
+    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="B10:T10"/>
+    <mergeCell ref="Z26:AE26"/>
+    <mergeCell ref="U9:X10"/>
+    <mergeCell ref="G20:AL20"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="W26:Y26"/>
+    <mergeCell ref="S24:V24"/>
   </mergeCells>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="98" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="98" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/invoice_template.xlsx
+++ b/templates/invoice_template.xlsx
@@ -34,30 +34,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
-    <t>{{BANK_CORR_NAME}}</t>
+    <t>{{КОРБАНК}}</t>
   </si>
   <si>
     <t>БИК</t>
   </si>
   <si>
-    <t>{{BANK_CORR_BIK}}</t>
+    <t>{{КОРБАНК_БИК}}</t>
   </si>
   <si>
     <t>Сч. №</t>
   </si>
   <si>
-    <t>{{BANK_CORR_ACC}}</t>
+    <t>{{КОРБАНК_КОРРСЧЕТ}}</t>
   </si>
   <si>
     <t>Банк-корреспондент</t>
   </si>
   <si>
-    <t>{{BANK_BEN_NAME}}</t>
+    <t>{{БАНК}}</t>
   </si>
   <si>
-    <t>{{BANK_BEN_LINE2}}</t>
+    <t>{{БАНК_БИК}}</t>
   </si>
   <si>
     <t>Банк получателя</t>
@@ -66,16 +66,16 @@
     <t>ИНН</t>
   </si>
   <si>
-    <t>{{BANK_BEN_INN}}</t>
+    <t>{{КОМПАНИЯ_ИНН}}</t>
   </si>
   <si>
     <t xml:space="preserve">КПП  </t>
   </si>
   <si>
-    <t>{{ACCOUNT_NUMBER}}</t>
+    <t>{{СЧЕТ}}</t>
   </si>
   <si>
-    <t>ОсОО "Авто Континент"</t>
+    <t>{{КОМПАНИЯ}}</t>
   </si>
   <si>
     <t>Получатель</t>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>ОсОО "Авто Континент", ИНН: 01905202610324, ИНН РФ: 9909768607, ОКПО: 34942535, Кыргызская Республика, г. Бишкек, Октябрьский район, ул. Матросова, д. 58, Неж.Пом. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{БАНК_КОРРСЧЕТ}}</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1230,9 @@
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="22"/>
-      <c r="Y9" s="32"/>
+      <c r="Y9" s="32" t="s">
+        <v>43</v>
+      </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AB9" s="16"/>
